--- a/TestData/Settings_TestData.xlsx
+++ b/TestData/Settings_TestData.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -472,9 +472,6 @@
           <t>12345678</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -537,6 +534,38 @@
       <c r="F4" t="inlineStr">
         <is>
           <t>EMPTY</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A number that is not a number</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>lawma195.infinity@gmail.com</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>12345678</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>abcdef</t>
         </is>
       </c>
     </row>
